--- a/exports_hebdomadaires/export_2025-10-06.xlsx
+++ b/exports_hebdomadaires/export_2025-10-06.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG23" t="n">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG27" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG29" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG33" t="n">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG35" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG36" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG38" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG40" t="n">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG41" t="n">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG43" t="n">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG47" t="n">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG51" t="n">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG53" t="n">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG54" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG56" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG58" t="n">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG60" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG61" t="n">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG65" t="n">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG68" t="n">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG69" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG79" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG84" t="n">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG91" t="n">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG92" t="n">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG94" t="n">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG95" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG96" t="n">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG99" t="n">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG102" t="n">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG109" t="n">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG112" t="n">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG116" t="n">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG117" t="n">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG118" t="n">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG123" t="n">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG125" t="n">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG128" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG137" t="n">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG140" t="n">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG141" t="n">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG144" t="n">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG149" t="n">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG152" t="n">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG154" t="n">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG158" t="n">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AF163" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG163" t="n">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="AF165" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG165" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG168" t="n">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="AF169" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG169" t="n">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="AF173" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG173" t="n">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG175" t="n">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="AF176" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG176" t="n">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AF181" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG181" t="n">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG182" t="n">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG183" t="n">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG186" t="n">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG187" t="n">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG189" t="n">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG197" t="n">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG199" t="n">
@@ -22009,7 +22009,7 @@
       </c>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG200" t="n">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG207" t="n">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG209" t="n">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG210" t="n">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG215" t="n">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG216" t="n">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG223" t="n">
@@ -24653,7 +24653,7 @@
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG225" t="n">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG227" t="n">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG230" t="n">
@@ -25753,7 +25753,7 @@
       </c>
       <c r="AF235" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG235" t="n">
@@ -26062,7 +26062,7 @@
       </c>
       <c r="AF238" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG238" t="n">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="AF248" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG248" t="n">
@@ -27346,7 +27346,7 @@
       </c>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG250" t="n">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="AF251" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG251" t="n">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="AF253" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG253" t="n">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="AF256" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG256" t="n">
@@ -28558,7 +28558,7 @@
       </c>
       <c r="AF261" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG261" t="n">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="AF266" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG266" t="n">
@@ -29313,7 +29313,7 @@
       </c>
       <c r="AF268" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG268" t="n">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="AF269" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG269" t="n">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="AF270" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG270" t="n">
@@ -29739,7 +29739,7 @@
       </c>
       <c r="AF272" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG272" t="n">
@@ -30289,7 +30289,7 @@
       </c>
       <c r="AF277" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG277" t="n">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="AF278" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG278" t="n">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="AF281" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG281" t="n">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AF294" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG294" t="n">
@@ -32179,7 +32179,7 @@
       </c>
       <c r="AF295" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG295" t="n">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AF297" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG297" t="n">
@@ -33764,7 +33764,7 @@
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG310" t="n">
@@ -34086,7 +34086,7 @@
       </c>
       <c r="AF313" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG313" t="n">
@@ -34198,7 +34198,7 @@
       </c>
       <c r="AF314" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG314" t="n">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="AF317" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG317" t="n">
@@ -34650,7 +34650,7 @@
       </c>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG318" t="n">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="AF326" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG326" t="n">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AF327" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG327" t="n">
@@ -35793,7 +35793,7 @@
       </c>
       <c r="AF329" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG329" t="n">
@@ -35897,7 +35897,7 @@
       </c>
       <c r="AF330" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG330" t="n">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="AF331" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG331" t="n">
@@ -36105,7 +36105,7 @@
       </c>
       <c r="AF332" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG332" t="n">
@@ -36313,7 +36313,7 @@
       </c>
       <c r="AF334" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG334" t="n">
@@ -36785,7 +36785,7 @@
       </c>
       <c r="AF338" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG338" t="n">
@@ -36889,7 +36889,7 @@
       </c>
       <c r="AF339" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG339" t="n">
@@ -37216,7 +37216,7 @@
       </c>
       <c r="AF342" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG342" t="n">
@@ -37629,7 +37629,7 @@
       </c>
       <c r="AF346" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG346" t="n">
@@ -38276,7 +38276,7 @@
       </c>
       <c r="AF352" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG352" t="n">
@@ -38385,7 +38385,7 @@
       </c>
       <c r="AF353" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG353" t="n">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG354" t="n">
@@ -38601,7 +38601,7 @@
       </c>
       <c r="AF355" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG355" t="n">
@@ -39136,7 +39136,7 @@
       </c>
       <c r="AF360" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG360" t="n">
@@ -39245,7 +39245,7 @@
       </c>
       <c r="AF361" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG361" t="n">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="AF362" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG362" t="n">
@@ -39785,7 +39785,7 @@
       </c>
       <c r="AF366" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG366" t="n">
@@ -40662,7 +40662,7 @@
       </c>
       <c r="AF374" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG374" t="n">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="AF375" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG375" t="n">
@@ -41762,7 +41762,7 @@
       </c>
       <c r="AF384" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG384" t="n">
@@ -42175,7 +42175,7 @@
       </c>
       <c r="AF388" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG388" t="n">
@@ -42852,7 +42852,7 @@
       </c>
       <c r="AF394" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG394" t="n">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AF395" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG395" t="n">
@@ -43068,7 +43068,7 @@
       </c>
       <c r="AF396" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG396" t="n">
@@ -44378,7 +44378,7 @@
       </c>
       <c r="AF408" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG408" t="n">
@@ -44702,7 +44702,7 @@
       </c>
       <c r="AF411" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG411" t="n">
@@ -44806,7 +44806,7 @@
       </c>
       <c r="AF412" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG412" t="n">
@@ -44910,7 +44910,7 @@
       </c>
       <c r="AF413" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG413" t="n">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AF415" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG415" t="n">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="AF417" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG417" t="n">
@@ -45782,7 +45782,7 @@
       </c>
       <c r="AF421" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG421" t="n">
@@ -46109,7 +46109,7 @@
       </c>
       <c r="AF424" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG424" t="n">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AF425" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG425" t="n">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AF426" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG426" t="n">
@@ -46649,7 +46649,7 @@
       </c>
       <c r="AF429" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG429" t="n">
@@ -46958,7 +46958,7 @@
       </c>
       <c r="AF432" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG432" t="n">
@@ -47348,7 +47348,7 @@
       </c>
       <c r="AF436" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG436" t="n">
@@ -47792,7 +47792,7 @@
       </c>
       <c r="AF440" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG440" t="n">
@@ -47896,7 +47896,7 @@
       </c>
       <c r="AF441" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG441" t="n">
@@ -48104,7 +48104,7 @@
       </c>
       <c r="AF443" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG443" t="n">
@@ -48778,7 +48778,7 @@
       </c>
       <c r="AF449" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG449" t="n">
@@ -49857,7 +49857,7 @@
       </c>
       <c r="AF459" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG459" t="n">
@@ -50199,7 +50199,7 @@
       </c>
       <c r="AF462" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG462" t="n">
@@ -50747,7 +50747,7 @@
       </c>
       <c r="AF467" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG467" t="n">
@@ -50851,7 +50851,7 @@
       </c>
       <c r="AF468" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG468" t="n">
@@ -51059,7 +51059,7 @@
       </c>
       <c r="AF470" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG470" t="n">
@@ -51368,7 +51368,7 @@
       </c>
       <c r="AF473" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG473" t="n">
@@ -51472,7 +51472,7 @@
       </c>
       <c r="AF474" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG474" t="n">
@@ -51584,7 +51584,7 @@
       </c>
       <c r="AF475" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG475" t="n">
@@ -51696,7 +51696,7 @@
       </c>
       <c r="AF476" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG476" t="n">
@@ -51808,7 +51808,7 @@
       </c>
       <c r="AF477" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG477" t="n">
@@ -52039,7 +52039,7 @@
       </c>
       <c r="AF479" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG479" t="n">
@@ -52454,7 +52454,7 @@
       </c>
       <c r="AF483" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG483" t="n">
@@ -52654,7 +52654,7 @@
       </c>
       <c r="AF485" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG485" t="n">
@@ -52766,7 +52766,7 @@
       </c>
       <c r="AF486" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG486" t="n">
@@ -52971,7 +52971,7 @@
       </c>
       <c r="AF488" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG488" t="n">
@@ -53088,7 +53088,7 @@
       </c>
       <c r="AF489" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG489" t="n">
@@ -53726,7 +53726,7 @@
       </c>
       <c r="AF495" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG495" t="n">
@@ -53954,7 +53954,7 @@
       </c>
       <c r="AF497" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG497" t="n">
@@ -54058,7 +54058,7 @@
       </c>
       <c r="AF498" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG498" t="n">
@@ -54271,7 +54271,7 @@
       </c>
       <c r="AF500" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG500" t="n">
@@ -54375,7 +54375,7 @@
       </c>
       <c r="AF501" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG501" t="n">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="AF505" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG505" t="n">
@@ -55006,7 +55006,7 @@
       </c>
       <c r="AF507" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG507" t="n">
@@ -55118,7 +55118,7 @@
       </c>
       <c r="AF508" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG508" t="n">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AF510" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG510" t="n">
@@ -55557,7 +55557,7 @@
       </c>
       <c r="AF512" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG512" t="n">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="AF518" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG518" t="n">
@@ -56415,7 +56415,7 @@
       </c>
       <c r="AF520" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG520" t="n">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="AF521" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG521" t="n">
@@ -56722,7 +56722,7 @@
       </c>
       <c r="AF523" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG523" t="n">
@@ -56826,7 +56826,7 @@
       </c>
       <c r="AF524" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG524" t="n">
@@ -57376,7 +57376,7 @@
       </c>
       <c r="AF529" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG529" t="n">
@@ -57923,7 +57923,7 @@
       </c>
       <c r="AF534" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG534" t="n">
@@ -58027,7 +58027,7 @@
       </c>
       <c r="AF535" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG535" t="n">
@@ -58594,7 +58594,7 @@
       </c>
       <c r="AF540" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG540" t="n">
@@ -59113,7 +59113,7 @@
       </c>
       <c r="AF545" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG545" t="n">
@@ -59326,7 +59326,7 @@
       </c>
       <c r="AF547" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG547" t="n">
@@ -59630,7 +59630,7 @@
       </c>
       <c r="AF550" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG550" t="n">
@@ -60045,7 +60045,7 @@
       </c>
       <c r="AF554" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG554" t="n">
@@ -60387,7 +60387,7 @@
       </c>
       <c r="AF557" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG557" t="n">
@@ -60595,7 +60595,7 @@
       </c>
       <c r="AF559" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG559" t="n">
@@ -62469,7 +62469,7 @@
       </c>
       <c r="AF576" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG576" t="n">
@@ -63263,7 +63263,7 @@
       </c>
       <c r="AF583" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG583" t="n">
@@ -63580,7 +63580,7 @@
       </c>
       <c r="AF586" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG586" t="n">
@@ -64013,7 +64013,7 @@
       </c>
       <c r="AF590" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG590" t="n">
@@ -64125,7 +64125,7 @@
       </c>
       <c r="AF591" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG591" t="n">
@@ -64237,7 +64237,7 @@
       </c>
       <c r="AF592" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG592" t="n">
@@ -64349,7 +64349,7 @@
       </c>
       <c r="AF593" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG593" t="n">
@@ -64699,7 +64699,7 @@
       </c>
       <c r="AF596" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG596" t="n">
@@ -65249,7 +65249,7 @@
       </c>
       <c r="AF601" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG601" t="n">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AF602" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG602" t="n">
@@ -66599,7 +66599,7 @@
       </c>
       <c r="AF613" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG613" t="n">
@@ -67030,7 +67030,7 @@
       </c>
       <c r="AF617" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG617" t="n">
@@ -67715,7 +67715,7 @@
       </c>
       <c r="AF623" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG623" t="n">
@@ -68161,7 +68161,7 @@
       </c>
       <c r="AF627" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG627" t="n">
@@ -69520,7 +69520,7 @@
       </c>
       <c r="AF639" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG639" t="n">
@@ -69624,7 +69624,7 @@
       </c>
       <c r="AF640" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG640" t="n">
@@ -70321,7 +70321,7 @@
       </c>
       <c r="AF646" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG646" t="n">
@@ -70557,7 +70557,7 @@
       </c>
       <c r="AF648" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG648" t="n">
@@ -71413,7 +71413,7 @@
       </c>
       <c r="AF656" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG656" t="n">
@@ -71631,7 +71631,7 @@
       </c>
       <c r="AF658" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG658" t="n">
@@ -71839,7 +71839,7 @@
       </c>
       <c r="AF660" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG660" t="n">
@@ -71948,7 +71948,7 @@
       </c>
       <c r="AF661" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG661" t="n">
@@ -72171,7 +72171,7 @@
       </c>
       <c r="AF663" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG663" t="n">
@@ -73105,7 +73105,7 @@
       </c>
       <c r="AF672" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG672" t="n">
@@ -73455,7 +73455,7 @@
       </c>
       <c r="AF675" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG675" t="n">
@@ -73774,7 +73774,7 @@
       </c>
       <c r="AF678" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG678" t="n">
@@ -73878,7 +73878,7 @@
       </c>
       <c r="AF679" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG679" t="n">
@@ -74304,7 +74304,7 @@
       </c>
       <c r="AF683" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG683" t="n">
@@ -74504,7 +74504,7 @@
       </c>
       <c r="AF685" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG685" t="n">
@@ -74948,7 +74948,7 @@
       </c>
       <c r="AF689" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG689" t="n">
@@ -75465,7 +75465,7 @@
       </c>
       <c r="AF694" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG694" t="n">
@@ -75852,7 +75852,7 @@
       </c>
       <c r="AF698" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG698" t="n">
@@ -75964,7 +75964,7 @@
       </c>
       <c r="AF699" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG699" t="n">
@@ -76519,7 +76519,7 @@
       </c>
       <c r="AF704" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG704" t="n">
@@ -76719,7 +76719,7 @@
       </c>
       <c r="AF706" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG706" t="n">
@@ -77205,7 +77205,7 @@
       </c>
       <c r="AF711" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG711" t="n">
@@ -77758,7 +77758,7 @@
       </c>
       <c r="AF716" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG716" t="n">
@@ -78163,7 +78163,7 @@
       </c>
       <c r="AF720" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG720" t="n">
@@ -78267,7 +78267,7 @@
       </c>
       <c r="AF721" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG721" t="n">
@@ -79012,7 +79012,7 @@
       </c>
       <c r="AF728" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG728" t="n">
@@ -79311,7 +79311,7 @@
       </c>
       <c r="AF731" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG731" t="n">
@@ -79977,7 +79977,7 @@
       </c>
       <c r="AF737" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG737" t="n">
@@ -80195,7 +80195,7 @@
       </c>
       <c r="AF739" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG739" t="n">
@@ -80413,7 +80413,7 @@
       </c>
       <c r="AF741" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG741" t="n">
@@ -80517,7 +80517,7 @@
       </c>
       <c r="AF742" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG742" t="n">
@@ -80875,7 +80875,7 @@
       </c>
       <c r="AF745" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG745" t="n">
@@ -81098,7 +81098,7 @@
       </c>
       <c r="AF747" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG747" t="n">
@@ -81202,7 +81202,7 @@
       </c>
       <c r="AF748" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG748" t="n">
@@ -81402,7 +81402,7 @@
       </c>
       <c r="AF750" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG750" t="n">
@@ -81506,7 +81506,7 @@
       </c>
       <c r="AF751" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG751" t="n">
@@ -81615,7 +81615,7 @@
       </c>
       <c r="AF752" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG752" t="n">
@@ -82081,7 +82081,7 @@
       </c>
       <c r="AF756" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG756" t="n">
@@ -82548,7 +82548,7 @@
       </c>
       <c r="AF760" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG760" t="n">
@@ -83547,7 +83547,7 @@
       </c>
       <c r="AF769" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG769" t="n">
@@ -83656,7 +83656,7 @@
       </c>
       <c r="AF770" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG770" t="n">
@@ -84120,7 +84120,7 @@
       </c>
       <c r="AF774" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG774" t="n">
@@ -84232,7 +84232,7 @@
       </c>
       <c r="AF775" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG775" t="n">
@@ -84577,7 +84577,7 @@
       </c>
       <c r="AF778" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG778" t="n">
@@ -85026,7 +85026,7 @@
       </c>
       <c r="AF782" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG782" t="n">
@@ -85143,7 +85143,7 @@
       </c>
       <c r="AF783" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG783" t="n">
@@ -85260,7 +85260,7 @@
       </c>
       <c r="AF784" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG784" t="n">
@@ -85582,7 +85582,7 @@
       </c>
       <c r="AF787" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG787" t="n">
@@ -85790,7 +85790,7 @@
       </c>
       <c r="AF789" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG789" t="n">
@@ -86140,7 +86140,7 @@
       </c>
       <c r="AF792" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG792" t="n">
@@ -86447,7 +86447,7 @@
       </c>
       <c r="AF795" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG795" t="n">
@@ -86551,7 +86551,7 @@
       </c>
       <c r="AF796" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG796" t="n">
@@ -86655,7 +86655,7 @@
       </c>
       <c r="AF797" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG797" t="n">
@@ -86764,7 +86764,7 @@
       </c>
       <c r="AF798" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG798" t="n">
@@ -86873,7 +86873,7 @@
       </c>
       <c r="AF799" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG799" t="n">
@@ -86985,7 +86985,7 @@
       </c>
       <c r="AF800" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG800" t="n">
@@ -87208,7 +87208,7 @@
       </c>
       <c r="AF802" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG802" t="n">
@@ -87709,7 +87709,7 @@
       </c>
       <c r="AF807" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG807" t="n">
@@ -87813,7 +87813,7 @@
       </c>
       <c r="AF808" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG808" t="n">
@@ -88278,7 +88278,7 @@
       </c>
       <c r="AF812" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG812" t="n">
@@ -88732,7 +88732,7 @@
       </c>
       <c r="AF816" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG816" t="n">
@@ -88841,7 +88841,7 @@
       </c>
       <c r="AF817" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG817" t="n">
@@ -89041,7 +89041,7 @@
       </c>
       <c r="AF819" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG819" t="n">
@@ -89571,7 +89571,7 @@
       </c>
       <c r="AF824" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG824" t="n">
@@ -89683,7 +89683,7 @@
       </c>
       <c r="AF825" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG825" t="n">
@@ -89979,7 +89979,7 @@
       </c>
       <c r="AF828" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG828" t="n">
@@ -90083,7 +90083,7 @@
       </c>
       <c r="AF829" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG829" t="n">
